--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -501,6 +511,8 @@
           <t>Character</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -540,6 +552,8 @@
           <t>Skin</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -583,6 +597,8 @@
           <t>SkinAsset</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -622,6 +638,8 @@
           <t>Action</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -661,6 +679,8 @@
           <t>Item</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,47 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TbStatusEffect</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>StatusEffect</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>#StatusEffect.xlsx</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>StatusEffect</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,6 +723,47 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TbAbility</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>#Ability.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,12 +604,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TbAction</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>#Action.xlsx</t>
+          <t>#Item.xlsx</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -635,7 +635,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -645,12 +645,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbStatusEffect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>StatusEffect</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>#Item.xlsx</t>
+          <t>#StatusEffect.xlsx</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -676,7 +676,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>StatusEffect</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -686,12 +686,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TbStatusEffect</t>
+          <t>TbAbility</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>StatusEffect</t>
+          <t>Ability</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>#StatusEffect.xlsx</t>
+          <t>#Ability.xlsx</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -717,52 +717,11 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>StatusEffect</t>
+          <t>Ability</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TbAbility</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ability</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>#Ability.xlsx</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Ability</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>TbCharacter</t>
@@ -505,17 +504,13 @@
           <t>map</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Character</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>TbSkin</t>
@@ -546,17 +541,13 @@
           <t>map</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Skin</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>TbSkinAsset</t>
@@ -597,11 +588,8 @@
           <t>SkinAsset</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>TbItem</t>
@@ -632,17 +620,13 @@
           <t>map</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>TbStatusEffect</t>
@@ -673,17 +657,13 @@
           <t>map</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>StatusEffect</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>TbAbility</t>
@@ -714,14 +694,53 @@
           <t>map</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Ability</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TbCombatConfig</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CombatConfig</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>#CombatConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CombatConfig(전역 전투 튜닝, 서버 전용)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,6 +742,47 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TbCharacterLoadout</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CharacterLoadout</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>#CharacterLoadout.xlsx</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CharacterLoadout</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,7 +743,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>TbCharacterLoadout</t>
@@ -774,14 +773,56 @@
           <t>map</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>CharacterLoadout</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TbAbilityView</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AbilityView</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>#AbilityView.xlsx</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AbilityView</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,7 +780,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>TbAbilityView</t>
@@ -821,8 +820,51 @@
           <t>AbilityView</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TbStatusEffectView</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>StatusEffectView</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>#StatusEffectView.xlsx</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>StatusEffectView</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,7 +822,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>TbStatusEffectView</t>
@@ -863,8 +862,126 @@
           <t>StatusEffectView</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TbGameMode</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GameMode</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>#GameMode.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>c,s,m</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GameMode</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TbMap</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GameMap</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>#Map.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>c,s,m</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>GameMap</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TbQueue</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>#Queue.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>c,s,m</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,6 +983,41 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TbFlappyConfig</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FlappyConfig</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>#FlappyConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FlappyConfig(Flappy Race 튜닝, 클·서 공용)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,76 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TbPanchigiConfig</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PanchigiConfig</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>#PanchigiConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PanchigiConfig(판치기 튜닝)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TbPanchigiSetup</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PanchigiSetup</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>#PanchigiSetup.xlsx</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PanchigiSetup(인원별 판 구성)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,6 +1088,41 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TbSkydiveConfig</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SkydiveConfig</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>#SkydiveConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SkydiveConfig(스카이다이브 자세·스태미나 튜닝, 클서 공용)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
